--- a/new/260913.xlsx
+++ b/new/260913.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BE72F6-17DA-4377-81AE-160B759D4B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E4FD9AA-E3AF-4BB4-8A84-DBBE385FE107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4490" yWindow="2140" windowWidth="15030" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9960" yWindow="4110" windowWidth="15030" windowHeight="11170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
-    <sheet name="SheetX" sheetId="1" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
+    <sheet name="SheetX" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>sich an der Herausforderung beteiligt – und das tut sie auch.
 Küpper: Wie erklären Sie sich dann, dass es doch ab und zu immer mal wieder Diskussionen gibt, auch gerade jetzt in der aktuellen Situation?
@@ -188,18 +189,128 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>in dieses Qualifizierungsprogramm bringen, wo sie eben soweit fit gemacht werden, dass sie dann im Arbeitsmarkt in eine reguläre Ausbildung einsteigen können.
-Und das hat sich bewährt und wir sind froh, dass wir eben diese Plätze auch bereitstellen können.
-Denn wichtig ist, dass die Menschen, die es wollen, tatsächlich auch die Voraussetzungen schaffen, um dann im Arbeitsmarkt erfolgreich sein zu können.
-Hahne: Arbeiten die eigentlich nur in der Produktion oder auch in der Verwaltung?
-Mattes: Nein, die sind in der Produktion, und da können wir auch genau sehr schön im Prinzip abbilden, was die Leute können und was die Leute wollen, und das passt hervorragend zusammen.
- Protektionismus ist in einer immer vernetzteren Welt genau das Falsche Hahne: Sie sind nicht nur als Manager in einem deutsch-amerikanischen Konzern ein USA-Kenner, Sie waren schon als Jugendlicher das erste Mal in den USA bei einer Gastfamilie.
-Aktuell läuft ja dort der Präsidentschaftswahlkampf auf Hochtouren.
-Beide Kandidaten schlagen protektionistische Töne an.
-Sorgt Sie das einerseits als USA-Liebhaber, andererseits aber auch als Manager?
-Die USA sind ja immerhin auch der wichtigste Exportmarkt für Deutschland.
-Mattes: Grundsätzlich, ungeachtet jetzt des Präsidentschaftswahlkampfs, ist Protektionismus in einer immer vernetzteren Welt genau das Falsche.
-Freier und fairer Handel, offene Grenzen – aber wie ich sagte, fair auch was Währungsgestaltung angeht –, das ist etwas, was wir befürworten, was ich befürworte, was Ford befürwortet und was auch sicherlich für die USA schon immer etwas war.
+    <t>Und hier muss jeder Staatsanwalt frühzeitig wissen – nicht nur der Staatsanwalt, der sich in einer Spezialabteilung befindet –, muss sich jeder Staatsanwalt frühzeitig bewusst werden: Gibt es hier Erkenntnisse, die darauf hindeuten, dass es sich um einen rechtsextremistischen Hintergrund handelt?
+Und insoweit haben wir versucht, jeden Staatsanwalt und im Übrigen auch versucht, jeden Vollzugsbeamten – denn man muss auch im Strafvollzug erkennen: Jemand, der wegen eines Diebstahls, eines Ladendiebstahls sitzt, auch der kann einen rechtsextremistischen Hintergrund haben – frühzeitig diese Strukturen zu erkennen, um sie dann den zuständigen Behörden zu melden, damit sich daraus nichts verfestigt.
+Geuther: Es gab im vergangenen Jahr fast 1.500 politisch rechts motivierte Gewalttaten und darunter eine bisher nie gehabte Zahl von Angriffen auf Flüchtlingsunterkünfte.
+Wie gehen Sie als Generalbundesanwalt damit um?
+Frank: Für die Beobachtung von rechtsextremistischen Straftaten gibt es im Bundesamt für Verfassungsschutz das gemeinsame Extremismus- und Terrorismusabwehrzentrum rechts, in dem auch wir – die Bundesanwaltschaft – vertreten sind.
+In diesem Zentrum, das eine Plattform darstellt, in dem Polizeibehörden, Dienste, Nachrichtendienste, aber auch die Staatsanwaltschaft vertreten ist, werden solche Vorfälle gemeinsam bewertet.
+Wir, die Bundesanwaltschaft, schauen uns diese schwerwiegenden Straftaten, wenn sie ein bestimmtes Ausmaß erreicht haben, immer wieder an, um dort auch herauszufinden, ob sich Strukturen bilden.
+Das ist eine der Konsequenzen auch der Ergebnisse aus der Aufarbeitung NSU, dass wir verschiedene Strukturverfahren angelegt haben, um frühzeitig herauszufinden: Welche Entwicklungen spielen sich in bestimmten Bereichen ab?
+Wir haben – gerade, was die Anschläge auf die Flüchtlingsheime im letzten Jahr anbelangt – Strukturen, Verfahren geführt, um festzustellen: Gibt es Vernetzungen?
+Sind das nur Taten von Einzelpersonen oder von lokalen kleineren Gruppierungen?
+Oder hat sich da eine größere Vernetzungsstruktur gebildet?
+Findet da vielleicht eine Steuerung aus einem etwas größeren Ganzen statt?
+Wir haben auch im Blick, zusammen mit den Polizei- und den Verfassungsschutzbehörden: rechtsextremistische Musikgruppen.
+Wir haben im Blick besonders: rechtsextremistische Gefährder.
+Wir stehen insoweit in einem engen Kontakt und Austausch mit dem Bundeskriminalamt.
+Wir kriegen in regelmäßigen Abständen alle Gefährder aus dem rechtsextremistischen Bereich gemeldet, die wir dann wiederum mit unseren Erkenntnissen versuchen abzuklären.
+Nur, wenn man versucht, das Phänomen Bereich Rechtsextremismus ganzheitlich zu betrachten und unter allen möglichen Aspekten und Blickwinkeln auch zu durchleuchten, dann lässt sich frühzeitig verhindern, dass sich wieder eine neue Struktur NSU bildet.
+Das ist für uns sehr wichtig.
+Geuther: Jetzt haben wir über Rechtsextremismus gesprochen, vorher über den Islamismus, über eine Amok-Tat.
+Gleichzeitig waren laut Verfassungsschutzbericht auch Linksextremisten im vergangenen Jahr deutlich gewalttätiger als zuvor.
+Und man könnte auch weitergehen.
+Die Verrohung steigt offenbar insgesamt.
+Nicht nur in der Sprache im Internet, auch im öffentlichen Dienst, im Arbeitsamt oder in der Ausländerbehörde werden Mitarbeiter öfter angegriffen.
+Was kann Recht da überhaupt leisten?
+Frank: Es ist seit längerer Zeit zu erkennen, dass die Gewaltbereitschaft in Deutschland zugenommen hat.
+Und so, wie Sie es beschrieben haben, es beginnt zunächst einmal mit einer Verrohung der Sprache.
+Und es führt dann zu einer Verrohung auch in der körperlichen Auseinandersetzung.
+Seit Jahren steigt der Anteil von Gewaltstraftaten.
+Und auch, wenn man sich die Entwicklung innerhalb der Gewaltstraftaten anschaut, so findet man immer wieder einen Anstieg auch der Vehemenz von Gewalt.
+Recht – und das ist das Entscheidende und Wichtige von Recht – Recht muss immer durchgesetzt werden.
+Recht muss insoweit standhaft bleiben, denn sonst verliert das Recht seine Achtung.
+Wir haben in Deutschland Werte letztendlich immer durch Rechtsnormen versucht auch abzusichern und Werteentfaltung durch das Schaffen von Recht einen Rahmen zu geben.
+Und nur, wenn wir diesen Rechtsrahmen auch konsequent verteidigen – und dazu gehört eine konsequente Strafverfolgung – nur, wenn wir diesen Rechtsrahmen verteidigen, dann haben wir eine Chance, dass das Recht und damit auch die Werte erhalten bleiben.
+Geuther: Herr Generalbundesanwalt, vielen Dank für das Gespräch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每周采访-160904-Kolner</t>
+  </si>
+  <si>
+    <t>每周采访-160828-Frod</t>
+  </si>
+  <si>
+    <t>每周采访-160807-Bundesweh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每周采访-160731-Generalbundesanwalt</t>
+  </si>
+  <si>
+    <t>dass wir verschiedene Strukturverfahren angelegt haben, um frühzeitig herauszufinden: Welche Entwicklungen spielen sich in bestimmten Bereichen ab?
+Wir haben – gerade, was die Anschläge auf die Flüchtlingsheime im letzten Jahr anbelangt – Strukturen, Verfahren geführt, um festzustellen: Gibt es Vernetzungen?
+Sind das nur Taten von Einzelpersonen oder von lokalen kleineren Gruppierungen?
+Oder hat sich da eine größere Vernetzungsstruktur gebildet?
+Findet da vielleicht eine Steuerung aus einem etwas größeren Ganzen statt?
+Wir haben auch im Blick, zusammen mit den Polizei- und den Verfassungsschutzbehörden: rechtsextremistische Musikgruppen.
+Wir haben im Blick besonders: rechtsextremistische Gefährder.
+Wir stehen insoweit in einem engen Kontakt und Austausch mit dem Bundeskriminalamt.
+Wir kriegen in regelmäßigen Abständen alle Gefährder aus dem rechtsextremistischen Bereich gemeldet, die wir dann wiederum mit unseren Erkenntnissen versuchen abzuklären.
+Nur, wenn man versucht, das Phänomen Bereich Rechtsextremismus ganzheitlich zu betrachten und unter allen möglichen Aspekten und Blickwinkeln auch zu durchleuchten, dann lässt sich frühzeitig verhindern, dass sich wieder eine neue Struktur NSU bildet.
+Das ist für uns sehr wichtig.
+Geuther: Jetzt haben wir über Rechtsextremismus gesprochen, vorher über den Islamismus, über eine Amok-Tat.
+Gleichzeitig waren laut Verfassungsschutzbericht auch Linksextremisten im vergangenen Jahr deutlich gewalttätiger als zuvor.
+Und man könnte auch weitergehen.
+Die Verrohung steigt offenbar insgesamt.
+Nicht nur in der Sprache im Internet, auch im öffentlichen Dienst, im Arbeitsamt oder in der Ausländerbehörde werden Mitarbeiter öfter angegriffen.
+Was kann Recht da überhaupt leisten?
+Frank: Es ist seit längerer Zeit zu erkennen, dass die Gewaltbereitschaft in Deutschland zugenommen hat.
+Und so, wie Sie es beschrieben haben, es beginnt zunächst einmal mit einer Verrohung der Sprache.
+Und es führt dann zu einer Verrohung auch in der körperlichen Auseinandersetzung.
+Seit Jahren steigt der Anteil von Gewaltstraftaten.
+Und auch, wenn man sich die Entwicklung innerhalb der Gewaltstraftaten anschaut, so findet man immer wieder einen Anstieg auch der Vehemenz von Gewalt.
+Recht – und das ist das Entscheidende und Wichtige von Recht – Recht muss immer durchgesetzt werden.
+Recht muss insoweit standhaft bleiben, denn sonst verliert das Recht seine Achtung.
+Wir haben in Deutschland Werte letztendlich immer durch Rechtsnormen versucht auch abzusichern und Werteentfaltung durch das Schaffen von Recht einen Rahmen zu geben.
+Und nur, wenn wir diesen Rechtsrahmen auch konsequent verteidigen – und dazu gehört eine konsequente Strafverfolgung – nur, wenn wir diesen Rechtsrahmen verteidigen, dann haben wir eine Chance, dass das Recht und damit auch die Werte erhalten bleiben.
+Geuther: Herr Generalbundesanwalt, vielen Dank für das Gespräch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Detjen: Dann werfen wir am Ende des Gesprächs nochmal den Blick auf das konkrete Thema, das uns alle, das das Land im vergangenen Jahr am meisten beschäftigt hat.
+Vor einem Jahr um diese Zeit schwante den meisten, dass mit der Flüchtlingsbewegung eine riesige Aufgabe, eine Generationenaufgabe auf Bund, Länder, Kommunen zukommen.
+Wenn Sie jetzt Hamburg anschauen, was sich in diesem Jahr getan hat, ist das für Sie ein Anlass, gut gelaunt auf die Entwicklung zu schauen oder eher schlecht gelaunt?
+Scholz: Was letztes Jahr stattfand, war eine unglaubliche Herausforderung.
+Und – das, glaube ich, muss man auch ganz offen sagen – in Deutschland war nicht überall klar, wer wann wo ist und wer wohin kommen soll und wer wo aufgenommen wird.
+Mittlerweile sind viele Institutionen, insbesondere auch das Bundesamt für Migration und Flüchtlinge, massiv ausgebaut worden.
+Dieser Ausbauprozess ist noch nicht beendet, das muss nun bald erfolgen.
+Und wir müssen mit den gesetzlichen Änderungen, die wir ergriffen haben, mit all den Maßnahmen, die wir getroffen haben, vorbereitet sein auf solche Entwicklungen.
+Das muss das Ergebnis des letzten Jahres sein.
+Denn wir können ja nicht sicher sein, dass nicht irgendwann mal wieder eine große Zahl von Flüchtlingen kommt.
+Jetzt sieht es ein wenig danach aus, dass es weniger werden und wir uns jetzt auf die Aufgabe konzentrieren können, diejenigen, die länger bleiben werden, zu integrieren.
+Detjen: Nochmal der Blick konkret auf Hamburg.
+Was haben Sie geschafft in diesem Jahr?
+Scholz: Wir haben Tausende von Unterkunftsplätzen geschaffen, was nicht ganz einfach ist in einer Stadt, die sehr bebaut ist und relativ mehr Flüchtlinge aufnimmt als andere, weil bei der Verteilung der Flüchtlinge in Deutschland Bevölkerungszahl und Wirtschaftskraft eine Rolle spielen und nicht die Frage 'Wieviel Platz hat man so?
+'.
+Das haben wir aber gemeistert und haben uns auch über viele Standorte verständigt, haben mit vielen Bürgerinnen und Bürgern gesprochenen, verhandelt, haben unglaublich viel Unterstützung bekommen von denjenigen, die in den Flüchtlingsunterkünften helfen.
+Und wir haben sofort dafür gesorgt, dass mehr Angebote gemacht werden bei Krippen und Kitas, bei den Schulen, haben zusätzliche Lehrerinnen und Lehrer eingestellt, damit es ohne Beeinträchtigung des bisherigen Betriebs zu einer schnellen Integration der jungen Leute kommt.
+Wir haben uns sofort darauf konzentriert, diejenigen, die in dem Alter sind, in dem man zur Berufsschule geht, dort auszubilden, auch mit einer Berufsorientierung zu versehen.
+Und wir haben Angebote entwickelt, die für diejenigen, die erwachsen sind, eine Arbeitsmarktintegration in den Blick nehmen.
+Detjen: Und vieles ist noch zu tun.
+Würden Sie Ihren Bürgerinnen und Bürgern in Hamburg sagen:  Wir schaffen das ?
+Scholz: Wer realistisch ist, kann immer nur sagen: Wir können das schaffen.
+Aber die Bürgerinnen und Bürger haben einen großen Beitrag dazu geleistet, dass zusammen mit einer sehr engagierten Verwaltung wir ganz schön weit gekommen sind und uns jetzt an die nächsten Aufgaben machen.
+Detjen: Herr Bürgermeister, vielen Dank.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Schlagen sich da ein paar Genossen jetzt im Nachhinein in die Büsche?
+Oder wirft diese Affäre ein Schlaglicht auf eine für die Politik vielleicht typische Verkümmerung von menschlichen Beziehungen?
+geschrieben, das trug die Überschrift: Die Partei der schlechten Laune.
+Das bezog sich nicht auf die SPD, richtig?
+Scholz: Klar, das bezog sich auf die AfD. Detjen: Warum ist die für Sie die Partei der schlechten Laune?
+Scholz: der Eindruck erweckt wird, alles läuft schief und es geht in die falsche Richtung.
+Was machen wir mit unseren öffentlichen Haushalten?
+Wie statten wir die Bundeswehr und unsere Polizei gut aus?
+Was machen wir, um die Bildung zu verbessern an den Schulen?
+Wie setzen wir Forschung und Universitäten auf die richtige Spur?
+Also immer ganz konkrete Politik, bei der es darum geht: Wie können wir dafür sorgen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>und was auch sicherlich für die USA schon immer etwas war.
 Die USA war immer offen, offen in der Entwicklung neuer Ideen und diese dann auch in die Welt hinauszutragen und nicht nur für sich selber zu sorgen.
 Von daher gesehen bin ich überzeugt, dass es das richtige Mittel ist, weiterhin freien und fairen Handel und wenig Protektionismus zu fordern und zu fördern.
 Wir werden sehen, welcher der Kandidaten letztlich Präsidentin oder Präsident wird.
@@ -246,124 +357,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Und hier muss jeder Staatsanwalt frühzeitig wissen – nicht nur der Staatsanwalt, der sich in einer Spezialabteilung befindet –, muss sich jeder Staatsanwalt frühzeitig bewusst werden: Gibt es hier Erkenntnisse, die darauf hindeuten, dass es sich um einen rechtsextremistischen Hintergrund handelt?
-Und insoweit haben wir versucht, jeden Staatsanwalt und im Übrigen auch versucht, jeden Vollzugsbeamten – denn man muss auch im Strafvollzug erkennen: Jemand, der wegen eines Diebstahls, eines Ladendiebstahls sitzt, auch der kann einen rechtsextremistischen Hintergrund haben – frühzeitig diese Strukturen zu erkennen, um sie dann den zuständigen Behörden zu melden, damit sich daraus nichts verfestigt.
-Geuther: Es gab im vergangenen Jahr fast 1.500 politisch rechts motivierte Gewalttaten und darunter eine bisher nie gehabte Zahl von Angriffen auf Flüchtlingsunterkünfte.
-Wie gehen Sie als Generalbundesanwalt damit um?
-Frank: Für die Beobachtung von rechtsextremistischen Straftaten gibt es im Bundesamt für Verfassungsschutz das gemeinsame Extremismus- und Terrorismusabwehrzentrum rechts, in dem auch wir – die Bundesanwaltschaft – vertreten sind.
-In diesem Zentrum, das eine Plattform darstellt, in dem Polizeibehörden, Dienste, Nachrichtendienste, aber auch die Staatsanwaltschaft vertreten ist, werden solche Vorfälle gemeinsam bewertet.
-Wir, die Bundesanwaltschaft, schauen uns diese schwerwiegenden Straftaten, wenn sie ein bestimmtes Ausmaß erreicht haben, immer wieder an, um dort auch herauszufinden, ob sich Strukturen bilden.
-Das ist eine der Konsequenzen auch der Ergebnisse aus der Aufarbeitung NSU, dass wir verschiedene Strukturverfahren angelegt haben, um frühzeitig herauszufinden: Welche Entwicklungen spielen sich in bestimmten Bereichen ab?
-Wir haben – gerade, was die Anschläge auf die Flüchtlingsheime im letzten Jahr anbelangt – Strukturen, Verfahren geführt, um festzustellen: Gibt es Vernetzungen?
-Sind das nur Taten von Einzelpersonen oder von lokalen kleineren Gruppierungen?
-Oder hat sich da eine größere Vernetzungsstruktur gebildet?
-Findet da vielleicht eine Steuerung aus einem etwas größeren Ganzen statt?
-Wir haben auch im Blick, zusammen mit den Polizei- und den Verfassungsschutzbehörden: rechtsextremistische Musikgruppen.
-Wir haben im Blick besonders: rechtsextremistische Gefährder.
-Wir stehen insoweit in einem engen Kontakt und Austausch mit dem Bundeskriminalamt.
-Wir kriegen in regelmäßigen Abständen alle Gefährder aus dem rechtsextremistischen Bereich gemeldet, die wir dann wiederum mit unseren Erkenntnissen versuchen abzuklären.
-Nur, wenn man versucht, das Phänomen Bereich Rechtsextremismus ganzheitlich zu betrachten und unter allen möglichen Aspekten und Blickwinkeln auch zu durchleuchten, dann lässt sich frühzeitig verhindern, dass sich wieder eine neue Struktur NSU bildet.
-Das ist für uns sehr wichtig.
-Geuther: Jetzt haben wir über Rechtsextremismus gesprochen, vorher über den Islamismus, über eine Amok-Tat.
-Gleichzeitig waren laut Verfassungsschutzbericht auch Linksextremisten im vergangenen Jahr deutlich gewalttätiger als zuvor.
-Und man könnte auch weitergehen.
-Die Verrohung steigt offenbar insgesamt.
-Nicht nur in der Sprache im Internet, auch im öffentlichen Dienst, im Arbeitsamt oder in der Ausländerbehörde werden Mitarbeiter öfter angegriffen.
-Was kann Recht da überhaupt leisten?
-Frank: Es ist seit längerer Zeit zu erkennen, dass die Gewaltbereitschaft in Deutschland zugenommen hat.
-Und so, wie Sie es beschrieben haben, es beginnt zunächst einmal mit einer Verrohung der Sprache.
-Und es führt dann zu einer Verrohung auch in der körperlichen Auseinandersetzung.
-Seit Jahren steigt der Anteil von Gewaltstraftaten.
-Und auch, wenn man sich die Entwicklung innerhalb der Gewaltstraftaten anschaut, so findet man immer wieder einen Anstieg auch der Vehemenz von Gewalt.
-Recht – und das ist das Entscheidende und Wichtige von Recht – Recht muss immer durchgesetzt werden.
-Recht muss insoweit standhaft bleiben, denn sonst verliert das Recht seine Achtung.
-Wir haben in Deutschland Werte letztendlich immer durch Rechtsnormen versucht auch abzusichern und Werteentfaltung durch das Schaffen von Recht einen Rahmen zu geben.
-Und nur, wenn wir diesen Rechtsrahmen auch konsequent verteidigen – und dazu gehört eine konsequente Strafverfolgung – nur, wenn wir diesen Rechtsrahmen verteidigen, dann haben wir eine Chance, dass das Recht und damit auch die Werte erhalten bleiben.
-Geuther: Herr Generalbundesanwalt, vielen Dank für das Gespräch</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每周采访-160904-Kolner</t>
-  </si>
-  <si>
-    <t>每周采访-160828-Frod</t>
-  </si>
-  <si>
-    <t>每周采访-160807-Bundesweh</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每周采访-160731-Generalbundesanwalt</t>
-  </si>
-  <si>
-    <t>dass wir verschiedene Strukturverfahren angelegt haben, um frühzeitig herauszufinden: Welche Entwicklungen spielen sich in bestimmten Bereichen ab?
-Wir haben – gerade, was die Anschläge auf die Flüchtlingsheime im letzten Jahr anbelangt – Strukturen, Verfahren geführt, um festzustellen: Gibt es Vernetzungen?
-Sind das nur Taten von Einzelpersonen oder von lokalen kleineren Gruppierungen?
-Oder hat sich da eine größere Vernetzungsstruktur gebildet?
-Findet da vielleicht eine Steuerung aus einem etwas größeren Ganzen statt?
-Wir haben auch im Blick, zusammen mit den Polizei- und den Verfassungsschutzbehörden: rechtsextremistische Musikgruppen.
-Wir haben im Blick besonders: rechtsextremistische Gefährder.
-Wir stehen insoweit in einem engen Kontakt und Austausch mit dem Bundeskriminalamt.
-Wir kriegen in regelmäßigen Abständen alle Gefährder aus dem rechtsextremistischen Bereich gemeldet, die wir dann wiederum mit unseren Erkenntnissen versuchen abzuklären.
-Nur, wenn man versucht, das Phänomen Bereich Rechtsextremismus ganzheitlich zu betrachten und unter allen möglichen Aspekten und Blickwinkeln auch zu durchleuchten, dann lässt sich frühzeitig verhindern, dass sich wieder eine neue Struktur NSU bildet.
-Das ist für uns sehr wichtig.
-Geuther: Jetzt haben wir über Rechtsextremismus gesprochen, vorher über den Islamismus, über eine Amok-Tat.
-Gleichzeitig waren laut Verfassungsschutzbericht auch Linksextremisten im vergangenen Jahr deutlich gewalttätiger als zuvor.
-Und man könnte auch weitergehen.
-Die Verrohung steigt offenbar insgesamt.
-Nicht nur in der Sprache im Internet, auch im öffentlichen Dienst, im Arbeitsamt oder in der Ausländerbehörde werden Mitarbeiter öfter angegriffen.
-Was kann Recht da überhaupt leisten?
-Frank: Es ist seit längerer Zeit zu erkennen, dass die Gewaltbereitschaft in Deutschland zugenommen hat.
-Und so, wie Sie es beschrieben haben, es beginnt zunächst einmal mit einer Verrohung der Sprache.
-Und es führt dann zu einer Verrohung auch in der körperlichen Auseinandersetzung.
-Seit Jahren steigt der Anteil von Gewaltstraftaten.
-Und auch, wenn man sich die Entwicklung innerhalb der Gewaltstraftaten anschaut, so findet man immer wieder einen Anstieg auch der Vehemenz von Gewalt.
-Recht – und das ist das Entscheidende und Wichtige von Recht – Recht muss immer durchgesetzt werden.
-Recht muss insoweit standhaft bleiben, denn sonst verliert das Recht seine Achtung.
-Wir haben in Deutschland Werte letztendlich immer durch Rechtsnormen versucht auch abzusichern und Werteentfaltung durch das Schaffen von Recht einen Rahmen zu geben.
-Und nur, wenn wir diesen Rechtsrahmen auch konsequent verteidigen – und dazu gehört eine konsequente Strafverfolgung – nur, wenn wir diesen Rechtsrahmen verteidigen, dann haben wir eine Chance, dass das Recht und damit auch die Werte erhalten bleiben.
-Geuther: Herr Generalbundesanwalt, vielen Dank für das Gespräch</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Detjen: Dann werfen wir am Ende des Gesprächs nochmal den Blick auf das konkrete Thema, das uns alle, das das Land im vergangenen Jahr am meisten beschäftigt hat.
-Vor einem Jahr um diese Zeit schwante den meisten, dass mit der Flüchtlingsbewegung eine riesige Aufgabe, eine Generationenaufgabe auf Bund, Länder, Kommunen zukommen.
-Wenn Sie jetzt Hamburg anschauen, was sich in diesem Jahr getan hat, ist das für Sie ein Anlass, gut gelaunt auf die Entwicklung zu schauen oder eher schlecht gelaunt?
-Scholz: Was letztes Jahr stattfand, war eine unglaubliche Herausforderung.
-Und – das, glaube ich, muss man auch ganz offen sagen – in Deutschland war nicht überall klar, wer wann wo ist und wer wohin kommen soll und wer wo aufgenommen wird.
-Mittlerweile sind viele Institutionen, insbesondere auch das Bundesamt für Migration und Flüchtlinge, massiv ausgebaut worden.
-Dieser Ausbauprozess ist noch nicht beendet, das muss nun bald erfolgen.
-Und wir müssen mit den gesetzlichen Änderungen, die wir ergriffen haben, mit all den Maßnahmen, die wir getroffen haben, vorbereitet sein auf solche Entwicklungen.
-Das muss das Ergebnis des letzten Jahres sein.
-Denn wir können ja nicht sicher sein, dass nicht irgendwann mal wieder eine große Zahl von Flüchtlingen kommt.
-Jetzt sieht es ein wenig danach aus, dass es weniger werden und wir uns jetzt auf die Aufgabe konzentrieren können, diejenigen, die länger bleiben werden, zu integrieren.
-Detjen: Nochmal der Blick konkret auf Hamburg.
-Was haben Sie geschafft in diesem Jahr?
-Scholz: Wir haben Tausende von Unterkunftsplätzen geschaffen, was nicht ganz einfach ist in einer Stadt, die sehr bebaut ist und relativ mehr Flüchtlinge aufnimmt als andere, weil bei der Verteilung der Flüchtlinge in Deutschland Bevölkerungszahl und Wirtschaftskraft eine Rolle spielen und nicht die Frage 'Wieviel Platz hat man so?
-'.
-Das haben wir aber gemeistert und haben uns auch über viele Standorte verständigt, haben mit vielen Bürgerinnen und Bürgern gesprochenen, verhandelt, haben unglaublich viel Unterstützung bekommen von denjenigen, die in den Flüchtlingsunterkünften helfen.
-Und wir haben sofort dafür gesorgt, dass mehr Angebote gemacht werden bei Krippen und Kitas, bei den Schulen, haben zusätzliche Lehrerinnen und Lehrer eingestellt, damit es ohne Beeinträchtigung des bisherigen Betriebs zu einer schnellen Integration der jungen Leute kommt.
-Wir haben uns sofort darauf konzentriert, diejenigen, die in dem Alter sind, in dem man zur Berufsschule geht, dort auszubilden, auch mit einer Berufsorientierung zu versehen.
-Und wir haben Angebote entwickelt, die für diejenigen, die erwachsen sind, eine Arbeitsmarktintegration in den Blick nehmen.
-Detjen: Und vieles ist noch zu tun.
-Würden Sie Ihren Bürgerinnen und Bürgern in Hamburg sagen:  Wir schaffen das ?
-Scholz: Wer realistisch ist, kann immer nur sagen: Wir können das schaffen.
-Aber die Bürgerinnen und Bürger haben einen großen Beitrag dazu geleistet, dass zusammen mit einer sehr engagierten Verwaltung wir ganz schön weit gekommen sind und uns jetzt an die nächsten Aufgaben machen.
-Detjen: Herr Bürgermeister, vielen Dank.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Schlagen sich da ein paar Genossen jetzt im Nachhinein in die Büsche?
-Oder wirft diese Affäre ein Schlaglicht auf eine für die Politik vielleicht typische Verkümmerung von menschlichen Beziehungen?
-geschrieben, das trug die Überschrift: Die Partei der schlechten Laune.
-Das bezog sich nicht auf die SPD, richtig?
-Scholz: Klar, das bezog sich auf die AfD. Detjen: Warum ist die für Sie die Partei der schlechten Laune?
-Scholz: der Eindruck erweckt wird, alles läuft schief und es geht in die falsche Richtung.
-Was machen wir mit unseren öffentlichen Haushalten?
-Wie statten wir die Bundeswehr und unsere Polizei gut aus?
-Was machen wir, um die Bildung zu verbessern an den Schulen?
-Wie setzen wir Forschung und Universitäten auf die richtige Spur?
-Also immer ganz konkrete Politik, bei der es darum geht: Wie können wir dafür sorgen</t>
+    <t xml:space="preserve">im Arbeitsmarkt in eine reguläre Ausbildung einsteigen können.
+Und das hat sich bewährt und wir sind froh, dass wir , tatsächlich auch die Voraussetzungen schaffen, um dann im Arbeitsmarkt erfolgreich sein zu können.
+Hahne: Arbeiten die eigentlich nur in der Produktion oder auch in der Verwaltung?
+Mattes: Nein, die sind in der Produktion.
+Sie sind nicht nur als Manager in einem deutsch-amerikanischen Konzern ein USA-Kenner.
+Aktuell läuft ja dort der Präsidentschaftswahlkampf auf Hochtouren.
+Beide Kandidaten schlagen protektionistische Töne an.
+Sorgt Sie das einerseits als USA-Liebhaber, ungeachtet jetzt des Präsidentschaftswahlkampfs, ist Protektionismus in einer immer vernetzteren Welt </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -700,7 +701,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -719,7 +720,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="392" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -729,6 +730,25 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D92C0922-5D1C-4A23-944E-3295CB561404}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="39.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="266" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -741,27 +761,27 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>0</v>

--- a/new/260913.xlsx
+++ b/new/260913.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E4FD9AA-E3AF-4BB4-8A84-DBBE385FE107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6043088D-6AEB-4265-9A83-0CFA64243BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9960" yWindow="4110" windowWidth="15030" windowHeight="11170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9960" yWindow="4110" windowWidth="15030" windowHeight="11170" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>

--- a/new/260913.xlsx
+++ b/new/260913.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6043088D-6AEB-4265-9A83-0CFA64243BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23EB0B0-81AB-4428-8F6B-62DD11326894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9960" yWindow="4110" windowWidth="15030" windowHeight="11170" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -239,36 +239,6 @@
     <t>每周采访-160731-Generalbundesanwalt</t>
   </si>
   <si>
-    <t>dass wir verschiedene Strukturverfahren angelegt haben, um frühzeitig herauszufinden: Welche Entwicklungen spielen sich in bestimmten Bereichen ab?
-Wir haben – gerade, was die Anschläge auf die Flüchtlingsheime im letzten Jahr anbelangt – Strukturen, Verfahren geführt, um festzustellen: Gibt es Vernetzungen?
-Sind das nur Taten von Einzelpersonen oder von lokalen kleineren Gruppierungen?
-Oder hat sich da eine größere Vernetzungsstruktur gebildet?
-Findet da vielleicht eine Steuerung aus einem etwas größeren Ganzen statt?
-Wir haben auch im Blick, zusammen mit den Polizei- und den Verfassungsschutzbehörden: rechtsextremistische Musikgruppen.
-Wir haben im Blick besonders: rechtsextremistische Gefährder.
-Wir stehen insoweit in einem engen Kontakt und Austausch mit dem Bundeskriminalamt.
-Wir kriegen in regelmäßigen Abständen alle Gefährder aus dem rechtsextremistischen Bereich gemeldet, die wir dann wiederum mit unseren Erkenntnissen versuchen abzuklären.
-Nur, wenn man versucht, das Phänomen Bereich Rechtsextremismus ganzheitlich zu betrachten und unter allen möglichen Aspekten und Blickwinkeln auch zu durchleuchten, dann lässt sich frühzeitig verhindern, dass sich wieder eine neue Struktur NSU bildet.
-Das ist für uns sehr wichtig.
-Geuther: Jetzt haben wir über Rechtsextremismus gesprochen, vorher über den Islamismus, über eine Amok-Tat.
-Gleichzeitig waren laut Verfassungsschutzbericht auch Linksextremisten im vergangenen Jahr deutlich gewalttätiger als zuvor.
-Und man könnte auch weitergehen.
-Die Verrohung steigt offenbar insgesamt.
-Nicht nur in der Sprache im Internet, auch im öffentlichen Dienst, im Arbeitsamt oder in der Ausländerbehörde werden Mitarbeiter öfter angegriffen.
-Was kann Recht da überhaupt leisten?
-Frank: Es ist seit längerer Zeit zu erkennen, dass die Gewaltbereitschaft in Deutschland zugenommen hat.
-Und so, wie Sie es beschrieben haben, es beginnt zunächst einmal mit einer Verrohung der Sprache.
-Und es führt dann zu einer Verrohung auch in der körperlichen Auseinandersetzung.
-Seit Jahren steigt der Anteil von Gewaltstraftaten.
-Und auch, wenn man sich die Entwicklung innerhalb der Gewaltstraftaten anschaut, so findet man immer wieder einen Anstieg auch der Vehemenz von Gewalt.
-Recht – und das ist das Entscheidende und Wichtige von Recht – Recht muss immer durchgesetzt werden.
-Recht muss insoweit standhaft bleiben, denn sonst verliert das Recht seine Achtung.
-Wir haben in Deutschland Werte letztendlich immer durch Rechtsnormen versucht auch abzusichern und Werteentfaltung durch das Schaffen von Recht einen Rahmen zu geben.
-Und nur, wenn wir diesen Rechtsrahmen auch konsequent verteidigen – und dazu gehört eine konsequente Strafverfolgung – nur, wenn wir diesen Rechtsrahmen verteidigen, dann haben wir eine Chance, dass das Recht und damit auch die Werte erhalten bleiben.
-Geuther: Herr Generalbundesanwalt, vielen Dank für das Gespräch</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Detjen: Dann werfen wir am Ende des Gesprächs nochmal den Blick auf das konkrete Thema, das uns alle, das das Land im vergangenen Jahr am meisten beschäftigt hat.
 Vor einem Jahr um diese Zeit schwante den meisten, dass mit der Flüchtlingsbewegung eine riesige Aufgabe, eine Generationenaufgabe auf Bund, Länder, Kommunen zukommen.
 Wenn Sie jetzt Hamburg anschauen, was sich in diesem Jahr getan hat, ist das für Sie ein Anlass, gut gelaunt auf die Entwicklung zu schauen oder eher schlecht gelaunt?
@@ -365,6 +335,14 @@
 Aktuell läuft ja dort der Präsidentschaftswahlkampf auf Hochtouren.
 Beide Kandidaten schlagen protektionistische Töne an.
 Sorgt Sie das einerseits als USA-Liebhaber, ungeachtet jetzt des Präsidentschaftswahlkampfs, ist Protektionismus in einer immer vernetzteren Welt </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>die darauf hindeuten, dass es sich um einen rechtsextremistischen Hintergrund handelt?
+versucht, jeden Vollzugsbeamten – denn man muss auch im Strafvollzug erkennen: Jemand, der wegen eines Diebstahls, eines Ladendiebstahls sitzt, auch der kann einen rechtsextremistischen Hintergrund haben – frühzeitig diese Strukturen zu erkennen, um sie dann den zuständigen Behörden zu melden, damit sich daraus nichts verfestigt.
+Geuther: Es gab im vergangenen Jahr fast 1.500 politisch rechts motivierte Gewalttaten und darunter eine bisher nie gehabte Zahl von Angriffen auf Flüchtlingsunterkünfte.
+gemeinsame Extremismus- und Terrorismusabwehrzentrum rechts, in dem auch wir – die Bundesanwaltschaft – vertreten sind.
+diese schwerwiegenden Straftaten</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -699,9 +677,9 @@
     <col min="1" max="1" width="39.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="252" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -720,7 +698,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="392" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -739,7 +717,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="266" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -778,10 +756,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>0</v>
